--- a/dados_coleta.xlsx
+++ b/dados_coleta.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,55 +436,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Turno</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Toneladas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Km_Total</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Km_Produtivo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Km_Improdutivo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Combustível</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Horas_Trabalhadas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Placa</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Qtd_Coletores</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Amostras_Validas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Viagens</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Produtividade (t/h)</t>
         </is>
@@ -496,39 +501,44 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>14210</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>65.18000000000001</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>36.79</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>28.4</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>45.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>8.9</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>TD-04</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
       <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
       <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
         <v>1596.73</v>
       </c>
     </row>
@@ -538,39 +548,44 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>8183.33</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>88.20999999999999</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>66.58</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>21.63</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>62</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>10.06</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>TD-07</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>813.09</v>
       </c>
     </row>
@@ -580,39 +595,44 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>13180.33</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>124.76</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>55.14</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>69.62</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>10.49</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>AN - 25</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
       <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
         <v>1256.23</v>
       </c>
     </row>
@@ -622,39 +642,44 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>19193.33</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>97.52</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>41.42</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>56.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>62.67</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>10.27</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>TD-05</t>
         </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
         <v>1869.09</v>
       </c>
     </row>
@@ -664,39 +689,44 @@
           <t>3001</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>19590</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>65.84</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>41.18</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>24.66</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>58</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>11.03</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>TD-06</t>
         </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>1776.67</v>
       </c>
     </row>
@@ -706,39 +736,44 @@
           <t>3002</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>16000</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>95</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>41.38</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>53.62</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>56.5</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>TD-05</t>
         </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>1756.39</v>
       </c>
     </row>
@@ -748,39 +783,44 @@
           <t>3003</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>10580</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>79.78</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>41.28</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>38.49</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>49</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>9.4</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>TD-04</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="n">
         <v>1</v>
       </c>
       <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>1125.53</v>
       </c>
     </row>
@@ -790,39 +830,44 @@
           <t>4001</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>16050</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>70.08</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>46.73</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>23.34</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>60</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>9.34</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>TD-07</t>
         </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>1718.24</v>
       </c>
     </row>
@@ -832,39 +877,44 @@
           <t>4004</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>17773.33</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>112.21</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>34.15</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>78.06</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>66.33</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>10.31</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>TD-05</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
       <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>1724.59</v>
       </c>
     </row>
@@ -874,39 +924,44 @@
           <t>5001</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>14230</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>68.55</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>37.88</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>30.67</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>50</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>8.74</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>TD-06</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>1628.92</v>
       </c>
     </row>
@@ -916,39 +971,44 @@
           <t>5002</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>14810</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>90.84</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>56.78</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>34.06</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>62.75</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>9.01</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>TD-05</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>4</v>
       </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
       <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
         <v>1643.87</v>
       </c>
     </row>
@@ -958,39 +1018,44 @@
           <t>5004</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>19208.12</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>106.98</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>56.47</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>50.5</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>63.25</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>10.12</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>TD-07</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>4</v>
       </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
       <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
         <v>1898.83</v>
       </c>
     </row>
@@ -1000,39 +1065,44 @@
           <t>5005</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DIURNO</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>19490</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>105.28</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>66.7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>38.56</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>71</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>11.27</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>TD-02</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
       <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
         <v>1729.78</v>
       </c>
     </row>
